--- a/data/trans_orig/Q20A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de veces que ha estado hospitalizado en los últimos 12 meses</t>
+          <t>Número medio de veces que la población ha estado hospitalizada en los últimos 12 meses (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,2</t>
+          <t>0,08; 0,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,18</t>
+          <t>0,1; 0,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,15</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,16</t>
+          <t>0,12; 0,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,17</t>
+          <t>0,06; 0,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,06</t>
+          <t>0,04; 0,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,15</t>
+          <t>0,04; 0,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,05</t>
+          <t>0,02; 0,06</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,03; 0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,32</t>
+          <t>0,05; 0,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,14</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,1</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,1</t>
+          <t>0,06; 0,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,18</t>
+          <t>0,06; 0,2</t>
         </is>
       </c>
     </row>
@@ -1146,17 +1146,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,06; 0,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,12</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_orig/Q20A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q20A-Estudios-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,12</t>
+          <t>0,11</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,2</t>
+          <t>0,09; 0,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,15</t>
+          <t>0,09; 0,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,13</t>
+          <t>0,08; 0,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,16</t>
+          <t>0,11; 0,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,14</t>
+          <t>0,09; 0,13</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,19</t>
+          <t>0,06; 0,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,1</t>
+          <t>0,05; 0,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,08</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,06</t>
+          <t>0,05; 0,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,08</t>
+          <t>0,06; 0,09</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>0,11</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -996,22 +996,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 0,14</t>
+          <t>0,04; 0,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,02; 0,06</t>
+          <t>0,01; 0,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,1</t>
+          <t>0,04; 0,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,28</t>
+          <t>0,05; 0,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,16</t>
+          <t>0,08; 0,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,13</t>
+          <t>0,07; 0,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,11</t>
+          <t>0,06; 0,12</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1083,27 +1083,27 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,12</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,09</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0,08</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,07</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1141,22 +1141,22 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,14</t>
+          <t>0,07; 0,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,05; 0,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,12</t>
+          <t>0,07; 0,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,12</t>
+          <t>0,09; 0,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,08</t>
+          <t>0,07; 0,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 0,09</t>
+          <t>0,07; 0,1</t>
         </is>
       </c>
     </row>
